--- a/reports/一级子公司B_利润表_2026-10.xlsx
+++ b/reports/一级子公司B_利润表_2026-10.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>52246939</v>
+        <v>68904685</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>15395991</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>148586843</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>216504</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>2094905</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>194364</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>1884687</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>161607</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>1569816</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>150596</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>1464440</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>86001</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>836474</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>64529</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>627186</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>52246939</v>
+        <v>68031084</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>14522390</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8656244</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>83657534</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1301564</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>12554283</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>652014</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>6280271</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4351324</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>41887729</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>435143</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>4190195</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>326030</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>3143150</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>542373</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>5238332</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>432863</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>4189632</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>52164321</v>
+        <v>51813641</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>491407289</v>
+        <v>491413347</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>82618</v>
+        <v>82065</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>824232</v>
+        <v>823920</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>967981</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>9413681</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>645007</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>6273270</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>48036426</v>
+        <v>61611630</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>27284283</v>
+        <v>34833517</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>161323</v>
+        <v>7773685</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1569132</v>
+        <v>75270009</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>27122960</v>
+        <v>27059832</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>261640432</v>
+        <v>261443937</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1627426</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>15693879</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>521713</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5024547</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>326370</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3141749</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>391599</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3771298</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>293367</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2828851</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>195197</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1885758</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>162269</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1571039</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1305156</v>
+        <v>1294929</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>12562477</v>
+        <v>12563047</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>43135</v>
+        <v>43074</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>418567</v>
+        <v>418562</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2691051</v>
+        <v>2688500</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>26152687</v>
+        <v>26147540</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>16295005</v>
+        <v>16125436</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>166837315</v>
+        <v>166739596</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2689492</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>26131791</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>460931</v>
+        <v>461815</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4633964</v>
+        <v>4629179</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>411451</v>
+        <v>411441</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4119066</v>
+        <v>4115826</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>31085</v>
+        <v>30936</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>309092</v>
+        <v>308818</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>139533</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1390407</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>285362</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2747976</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>93253</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>927855</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>69922</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>696096</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>116390</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1160248</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>406536</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3928562</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>61796</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>618490</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>46233</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>463641</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>76900</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>772316</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>53764</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>540348</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>38395</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>385819</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>30742</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>308603</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>23097</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>231463</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>4210513</v>
+        <v>7404868</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-121840</v>
+        <v>4882743</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>162832</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1569597</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>38831</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>386457</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>62166</v>
+        <v>62170</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>618173</v>
+        <v>618602</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>4148347</v>
+        <v>7505530</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1843052</v>
+        <v>1861806</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>18533826</v>
+        <v>18563852</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>2305295</v>
+        <v>5643724</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>2305295</v>
+        <v>5643724</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>2305295</v>
+        <v>5643724</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>2305295</v>
+        <v>5643724</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>2305295</v>
+        <v>5643724</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
